--- a/data/trans_dic/P44A$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 24,61</t>
+          <t>4,51; 24,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 35,1</t>
+          <t>12,66; 35,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 45,03</t>
+          <t>22,62; 46,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 30,32</t>
+          <t>9,16; 31,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 34,34</t>
+          <t>16,43; 33,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 29,06</t>
+          <t>13,55; 28,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,81</t>
+          <t>0,19; 1,82</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 42,81</t>
+          <t>14,65; 42,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 28,51</t>
+          <t>9,69; 28,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 58,39</t>
+          <t>21,95; 59,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,32; 52,5</t>
+          <t>20,0; 52,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 42,25</t>
+          <t>20,28; 41,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 32,26</t>
+          <t>15,95; 31,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,16</t>
+          <t>0,08; 1,23</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 59,02</t>
+          <t>18,18; 57,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 73,33</t>
+          <t>16,55; 73,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 70,56</t>
+          <t>14,53; 72,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 38,99</t>
+          <t>4,0; 38,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 52,68</t>
+          <t>21,34; 55,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,91</t>
+          <t>9,85; 25,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 29,57</t>
+          <t>15,91; 30,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,04</t>
+          <t>0,06; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 45,08</t>
+          <t>27,07; 46,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 35,86</t>
+          <t>17,98; 36,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,12; 1,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 32,18</t>
+          <t>19,71; 32,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 30,36</t>
+          <t>18,83; 29,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,84</t>
+          <t>0,15; 0,84</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1939; 11088</t>
+          <t>2034; 11136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6548; 18153</t>
+          <t>6545; 18550</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4269</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13342; 28332</t>
+          <t>14233; 29187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5424; 18832</t>
+          <t>5690; 19277</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3270</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17621; 37074</t>
+          <t>17735; 36034</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15479; 33078</t>
+          <t>15427; 32324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>602; 5632</t>
+          <t>579; 5659</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7091; 21298</t>
+          <t>7288; 21238</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7908; 22260</t>
+          <t>7563; 22577</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7155</t>
+          <t>0; 7141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6897; 17776</t>
+          <t>6682; 18188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7404; 19132</t>
+          <t>7290; 19182</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4020</t>
+          <t>0; 4563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16377; 33877</t>
+          <t>16261; 33379</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18282; 36949</t>
+          <t>18272; 36446</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>619; 8524</t>
+          <t>623; 9000</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4966; 17083</t>
+          <t>5262; 16750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1484</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1204; 9158</t>
+          <t>2067; 9123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2287; 11391</t>
+          <t>2345; 11686</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1103; 10547</t>
+          <t>1082; 10384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9927; 23753</t>
+          <t>9622; 25074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1261</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10251; 27241</t>
+          <t>10773; 27710</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26132; 46946</t>
+          <t>25249; 48401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>576; 8074</t>
+          <t>488; 8392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27539; 47713</t>
+          <t>28655; 48710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21362; 41128</t>
+          <t>20627; 41624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>747; 5927</t>
+          <t>594; 5537</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42340; 69253</t>
+          <t>42415; 69319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52767; 83010</t>
+          <t>51476; 81324</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1982; 10556</t>
+          <t>1819; 10570</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 24,72</t>
+          <t>4,48; 24,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 35,87</t>
+          <t>12,55; 34,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,62; 46,39</t>
+          <t>21,63; 46,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 31,03</t>
+          <t>9,93; 30,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 33,37</t>
+          <t>16,02; 33,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 28,4</t>
+          <t>12,84; 28,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,82</t>
+          <t>0,17; 1,59</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,65; 42,69</t>
+          <t>14,34; 41,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 28,91</t>
+          <t>10,13; 27,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,18; 2,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,95; 59,75</t>
+          <t>21,36; 60,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 52,64</t>
+          <t>19,93; 51,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 41,63</t>
+          <t>20,09; 42,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 31,82</t>
+          <t>16,29; 32,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,23</t>
+          <t>0,23; 1,63</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,18; 57,87</t>
+          <t>17,11; 57,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 73,04</t>
+          <t>13,6; 73,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 72,39</t>
+          <t>14,35; 69,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 38,39</t>
+          <t>4,57; 44,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,34; 55,61</t>
+          <t>20,0; 53,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,34</t>
+          <t>9,48; 25,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 30,49</t>
+          <t>15,77; 29,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,08</t>
+          <t>0,21; 1,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,07; 46,02</t>
+          <t>25,9; 45,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 36,29</t>
+          <t>18,43; 36,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,16</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,71; 32,21</t>
+          <t>19,84; 32,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 29,74</t>
+          <t>18,86; 29,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,84</t>
+          <t>0,24; 0,96</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2217</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2034; 11136</t>
+          <t>2020; 10921</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6545; 18550</t>
+          <t>6491; 17979</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 3577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14233; 29187</t>
+          <t>13608; 29013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5690; 19277</t>
+          <t>6169; 18950</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17735; 36034</t>
+          <t>17297; 35677</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15427; 32324</t>
+          <t>14616; 32207</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>579; 5659</t>
+          <t>574; 5348</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3448</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7288; 21238</t>
+          <t>7132; 20732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7563; 22577</t>
+          <t>7909; 21566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7141</t>
+          <t>514; 6950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6682; 18188</t>
+          <t>6502; 18310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7290; 19182</t>
+          <t>7261; 18768</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16261; 33379</t>
+          <t>16106; 34141</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18272; 36446</t>
+          <t>18654; 37065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>623; 9000</t>
+          <t>1237; 8696</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5262; 16750</t>
+          <t>4953; 16693</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2067; 9123</t>
+          <t>1698; 9238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2345; 11686</t>
+          <t>2316; 11226</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1082; 10384</t>
+          <t>1237; 11945</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9622; 25074</t>
+          <t>9019; 24018</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10773; 27710</t>
+          <t>10363; 27833</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25249; 48401</t>
+          <t>25029; 46479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>488; 8392</t>
+          <t>1195; 8071</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28655; 48710</t>
+          <t>27408; 48542</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20627; 41624</t>
+          <t>21145; 41306</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>594; 5537</t>
+          <t>656; 5722</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42415; 69319</t>
+          <t>42697; 69718</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51476; 81324</t>
+          <t>51560; 80934</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1819; 10570</t>
+          <t>2644; 10540</t>
         </is>
       </c>
     </row>
